--- a/dados/excel/cargo_map.xlsx
+++ b/dados/excel/cargo_map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legenda — Famílias" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Legenda — Hierarquia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda — Famílias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda — Hierarquia" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$270</definedName>
@@ -801,7 +801,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="B4" s="39" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10480,7 +10480,7 @@
       </c>
       <c r="B5" s="40" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B7" s="42" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B8" s="43" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="B9" s="44" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="B10" s="45" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B11" s="46" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="B12" s="47" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="B13" s="48" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="B14" s="49" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="B3" s="50" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="B4" s="51" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="B5" s="52" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="B6" s="53" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="B7" s="54" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="B8" s="55" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>

--- a/dados/excel/cargo_map.xlsx
+++ b/dados/excel/cargo_map.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
